--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.03257695342435</v>
+        <v>9.755293754931456</v>
       </c>
       <c r="D2" t="n">
-        <v>5.587903856089018</v>
+        <v>0.9080343766144655</v>
       </c>
       <c r="E2" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F2" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.07318908768433</v>
+        <v>6.349393226748703</v>
       </c>
       <c r="D3" t="n">
-        <v>23.27455504901641</v>
+        <v>3.782115195465167</v>
       </c>
       <c r="E3" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.28237892661694</v>
+        <v>3.620886575575252</v>
       </c>
       <c r="D4" t="n">
-        <v>23.80226589413102</v>
+        <v>3.86786820779629</v>
       </c>
       <c r="E4" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.63372772326878</v>
+        <v>7.740480755031178</v>
       </c>
       <c r="D5" t="n">
-        <v>40.58714224606704</v>
+        <v>6.595410614985894</v>
       </c>
       <c r="E5" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.44618344422936</v>
+        <v>5.92250480968727</v>
       </c>
       <c r="D6" t="n">
-        <v>36.35787685797383</v>
+        <v>5.908154989420748</v>
       </c>
       <c r="E6" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.46952767687235</v>
+        <v>8.038798247491759</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73467912453342</v>
+        <v>5.644385357736681</v>
       </c>
       <c r="E7" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.05778075670437</v>
+        <v>6.67188937296446</v>
       </c>
       <c r="D8" t="n">
-        <v>32.24494233406433</v>
+        <v>5.239803129285455</v>
       </c>
       <c r="E8" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27266720019558</v>
+        <v>5.731808420031782</v>
       </c>
       <c r="D9" t="n">
-        <v>21.69352541647873</v>
+        <v>3.525197880177794</v>
       </c>
       <c r="E9" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F9" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>64.25631286128468</v>
+        <v>10.44165083995876</v>
       </c>
       <c r="D10" t="n">
-        <v>33.63943474923344</v>
+        <v>5.466408146750434</v>
       </c>
       <c r="E10" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F10" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.83418074107259</v>
+        <v>2.248054370424296</v>
       </c>
       <c r="D11" t="n">
-        <v>13.49509666329372</v>
+        <v>2.19295320778523</v>
       </c>
       <c r="E11" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.80352714789046</v>
+        <v>6.1430731615322</v>
       </c>
       <c r="D12" t="n">
-        <v>37.88713216528925</v>
+        <v>6.156658976859504</v>
       </c>
       <c r="E12" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>51.46894806611662</v>
+        <v>8.363704060743952</v>
       </c>
       <c r="D13" t="n">
-        <v>20.248494951508</v>
+        <v>3.29038042962005</v>
       </c>
       <c r="E13" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.65352961965569</v>
+        <v>7.093698563194049</v>
       </c>
       <c r="D14" t="n">
-        <v>43.44343367122637</v>
+        <v>7.059557971574285</v>
       </c>
       <c r="E14" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F14" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.46161316817654</v>
+        <v>4.625012139828688</v>
       </c>
       <c r="D15" t="n">
-        <v>27.36968813429591</v>
+        <v>4.447574321823086</v>
       </c>
       <c r="E15" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.35935300807277</v>
+        <v>5.908394863811826</v>
       </c>
       <c r="D16" t="n">
-        <v>35.44977056322731</v>
+        <v>5.760587716524438</v>
       </c>
       <c r="E16" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.81691198519835</v>
+        <v>6.145248197594732</v>
       </c>
       <c r="D17" t="n">
-        <v>36.70240013681891</v>
+        <v>5.964140022233073</v>
       </c>
       <c r="E17" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F17" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.77157398439857</v>
+        <v>8.087880772464768</v>
       </c>
       <c r="D18" t="n">
-        <v>11.92064501947084</v>
+        <v>1.937104815664012</v>
       </c>
       <c r="E18" t="n">
-        <v>12.26373167686405</v>
+        <v>1.992856397490408</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5775854871193</v>
+        <v>1.718857641656886</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
